--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121617067</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121788390</v>
+        <v>121788384</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121788376</v>
+        <v>121788390</v>
       </c>
       <c r="B4" t="n">
-        <v>57304</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102620</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121788384</v>
+        <v>121788376</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>57304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,25 +1171,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121788384</v>
+        <v>121788390</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121788390</v>
+        <v>121788376</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>57304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121788376</v>
+        <v>121788384</v>
       </c>
       <c r="B6" t="n">
-        <v>57304</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,25 +1171,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102620</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121788390</v>
+        <v>121788376</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102620</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121788376</v>
+        <v>121788390</v>
       </c>
       <c r="B4" t="n">
-        <v>57304</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102620</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1277,6 +1277,246 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121900528</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57726</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Göljemossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>521504</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6498658</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kristberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Eriksson, Tommy Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121900526</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Göljemossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>521504</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6498658</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kristberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Eriksson, Tommy Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121788376</v>
+        <v>121788390</v>
       </c>
       <c r="B3" t="n">
-        <v>57304</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102620</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121788390</v>
+        <v>121788376</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>57304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121788376</v>
+        <v>121788478</v>
       </c>
       <c r="B4" t="n">
-        <v>57304</v>
+        <v>57376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102620</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,7 +955,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -998,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121788478</v>
+        <v>121788384</v>
       </c>
       <c r="B5" t="n">
-        <v>57376</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,25 +1051,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1075,11 +1079,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121788384</v>
+        <v>121788376</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>57304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,25 +1171,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121900528</v>
+        <v>121900526</v>
       </c>
       <c r="B7" t="n">
-        <v>57726</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,20 +1291,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1312,10 +1312,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1395,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121900526</v>
+        <v>121900528</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>57726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,20 +1415,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1428,18 +1436,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121788390</v>
+        <v>121788384</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121788384</v>
+        <v>121788376</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>57304</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,25 +1051,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102620</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121788376</v>
+        <v>121788390</v>
       </c>
       <c r="B6" t="n">
-        <v>57304</v>
+        <v>57726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,16 +1175,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102620</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Eriksson, Tommy Eriksson</t>
+          <t>Tommy Eriksson, Anders Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Eriksson, Tommy Eriksson</t>
+          <t>Tommy Eriksson, Anders Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,6 +1397,130 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122426190</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57321</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergshult, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>521440</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6498546</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kristberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Åström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Åström, Sara Åström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -1282,7 +1282,7 @@
         <v>122051769</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>57295</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>122426190</v>
       </c>
       <c r="B8" t="n">
-        <v>57321</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -1297,11 +1297,6 @@
       <c r="E7" t="n">
         <v>100067</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Haliaeetus albicilla</t>
@@ -1416,11 +1411,6 @@
       </c>
       <c r="E8" t="n">
         <v>102620</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Hökuggla</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 25600-2022 artfynd.xlsx
+++ b/artfynd/A 25600-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,125 +1392,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>122426190</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>102620</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Surnia ulula</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bergshult, Ög</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>521440</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6498546</v>
-      </c>
-      <c r="S8" t="n">
-        <v>50</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Motala</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Kristberg</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Stefan Åström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Stefan Åström, Sara Åström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
